--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>4.3</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H4" t="n">
         <v>1.83</v>
@@ -1175,11 +1175,11 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.77</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.84</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="G4" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I4" t="n">
         <v>2.08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>5.2</v>
@@ -1154,13 +1154,13 @@
         <v>1.82</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -760,7 +760,7 @@
         <v>1.84</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
         <v>3.7</v>
@@ -769,7 +769,7 @@
         <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G4" t="n">
         <v>5.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="I4" t="n">
         <v>2.06</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
@@ -772,19 +772,19 @@
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
         <v>1.78</v>
@@ -793,134 +793,134 @@
         <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.88</v>
       </c>
       <c r="I4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="G2" t="n">
         <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -775,7 +775,7 @@
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -805,7 +805,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.86</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,19 +781,19 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
         <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
         <v>2.88</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
         <v>2.6</v>
       </c>
       <c r="I3" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -978,19 +978,19 @@
         <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="R3" t="n">
         <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
         <v>1.56</v>
@@ -999,16 +999,16 @@
         <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>23</v>
@@ -1023,7 +1023,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -1032,10 +1032,10 @@
         <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
         <v>42</v>
@@ -1065,10 +1065,10 @@
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1080,10 +1080,10 @@
         <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY3" t="n">
         <v>9.6</v>
@@ -1092,29 +1092,29 @@
         <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -1145,46 +1145,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
         <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1199,116 +1199,1862 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Shakhtar</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -766,13 +766,13 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
         <v>2.6</v>
@@ -999,7 +999,7 @@
         <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W3" t="n">
         <v>1.51</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="H4" t="n">
         <v>1.82</v>
@@ -1160,88 +1160,88 @@
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
         <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
         <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
         <v>150</v>
       </c>
       <c r="AK4" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AL4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM4" t="n">
         <v>160</v>
@@ -1250,65 +1250,65 @@
         <v>110</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>2.98</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="AS4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU4" t="n">
         <v>7</v>
       </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV4" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>26</v>
+        <v>3.95</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -1351,10 +1351,10 @@
         <v>3.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.29</v>
@@ -1378,22 +1378,22 @@
         <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
         <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
         <v>1.92</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
         <v>16.5</v>
@@ -1402,64 +1402,64 @@
         <v>30</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ5" t="n">
         <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
         <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
       </c>
       <c r="AQ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AT5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7.8</v>
@@ -1468,7 +1468,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
@@ -1480,7 +1480,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB5" t="n">
         <v>21</v>
@@ -1489,20 +1489,20 @@
         <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BF5" t="n">
         <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
         <v>4.4</v>
@@ -1551,13 +1551,13 @@
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
@@ -1566,13 +1566,13 @@
         <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
         <v>1.81</v>
@@ -1605,7 +1605,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>55</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
         <v>3.45</v>
       </c>
       <c r="H7" t="n">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
         <v>2.22</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="R7" t="n">
         <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,64 +1775,64 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
         <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
         <v>1.03</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J8" t="n">
         <v>3.45</v>
@@ -1945,16 +1945,16 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
         <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
         <v>1.33</v>
@@ -1963,7 +1963,7 @@
         <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
         <v>2.1</v>
@@ -1975,70 +1975,70 @@
         <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM8" t="n">
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
         <v>9.4</v>
@@ -2050,7 +2050,7 @@
         <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2062,29 +2062,29 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="G9" t="n">
         <v>1.99</v>
@@ -2124,13 +2124,13 @@
         <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,10 +2139,10 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
         <v>1.89</v>
@@ -2163,13 +2163,13 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="n">
         <v>16</v>
@@ -2178,7 +2178,7 @@
         <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB9" t="n">
         <v>8.800000000000001</v>
@@ -2199,19 +2199,19 @@
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
         <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
         <v>140</v>
@@ -2220,7 +2220,7 @@
         <v>15</v>
       </c>
       <c r="AO9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
         <v>12</v>
@@ -2229,13 +2229,13 @@
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
         <v>7.4</v>
@@ -2244,7 +2244,7 @@
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9" t="n">
         <v>19</v>
@@ -2265,20 +2265,20 @@
         <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
         <v>12.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -2333,10 +2333,10 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
         <v>2.04</v>
@@ -2351,10 +2351,10 @@
         <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
         <v>1.36</v>
@@ -2363,49 +2363,49 @@
         <v>1.84</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
         <v>18</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AI10" t="n">
         <v>50</v>
       </c>
-      <c r="AF10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
         <v>100</v>
@@ -2414,7 +2414,7 @@
         <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2423,10 +2423,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
         <v>9.4</v>
@@ -2435,44 +2435,44 @@
         <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BB10" t="n">
         <v>19</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
         <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H11" t="n">
         <v>3.55</v>
@@ -2521,7 +2521,7 @@
         <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
@@ -2554,34 +2554,34 @@
         <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -2590,83 +2590,83 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
         <v>29</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
         <v>32</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
         <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BB11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD11" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
         <v>44</v>
       </c>
       <c r="BF11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG11" t="n">
         <v>32</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>3.85</v>
@@ -2721,7 +2721,7 @@
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.34</v>
@@ -2733,7 +2733,7 @@
         <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
         <v>3.6</v>
@@ -2748,7 +2748,7 @@
         <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X12" t="n">
         <v>14</v>
@@ -2757,22 +2757,22 @@
         <v>16</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>18.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
         <v>11.5</v>
@@ -2784,7 +2784,7 @@
         <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ12" t="n">
         <v>22</v>
@@ -2796,22 +2796,22 @@
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN12" t="n">
         <v>13.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP12" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AS12" t="n">
         <v>38</v>
@@ -2820,47 +2820,47 @@
         <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
         <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
         <v>40</v>
       </c>
       <c r="BF12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG12" t="n">
         <v>32</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -2903,13 +2903,13 @@
         <v>5.7</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -2921,7 +2921,7 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
         <v>1.78</v>
@@ -2930,7 +2930,7 @@
         <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.83</v>
@@ -2945,85 +2945,85 @@
         <v>2.4</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
         <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN13" t="n">
         <v>8.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS13" t="n">
         <v>42</v>
       </c>
       <c r="AT13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
         <v>9</v>
       </c>
-      <c r="AU13" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AV13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>32</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY13" t="n">
         <v>9.4</v>
@@ -3041,20 +3041,20 @@
         <v>15</v>
       </c>
       <c r="BD13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
         <v>38</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
         <v>60</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>FC Shirak</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>BKMA Yerevan</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,22 +781,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS3" t="n">
         <v>4.2</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AT3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB3" t="n">
         <v>21</v>
       </c>
-      <c r="Y3" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC3" t="n">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
         <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.6</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9</v>
+        <v>2.82</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82</v>
+        <v>2.48</v>
       </c>
       <c r="I4" t="n">
-        <v>1.98</v>
+        <v>2.68</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD4" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM4" t="n">
         <v>90</v>
       </c>
-      <c r="AL4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>160</v>
-      </c>
       <c r="AN4" t="n">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>2.98</v>
-      </c>
       <c r="AR4" t="n">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="I5" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S5" t="n">
         <v>3.85</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="T5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC5" t="n">
         <v>4.4</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X5" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18</v>
-      </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>14.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>28</v>
+        <v>3.85</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
         <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD6" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>17</v>
-      </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>20</v>
       </c>
       <c r="AL6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO6" t="n">
         <v>36</v>
       </c>
-      <c r="AM6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>50</v>
-      </c>
       <c r="AP6" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV6" t="n">
         <v>14</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AW6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD6" t="n">
         <v>28</v>
       </c>
-      <c r="AS6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="BE6" t="n">
         <v>15.5</v>
       </c>
-      <c r="AW6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX6" t="n">
+      <c r="BF6" t="n">
         <v>11</v>
       </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA6" t="n">
+      <c r="BG6" t="n">
         <v>30</v>
       </c>
-      <c r="BB6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>44</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.76</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="P7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.29</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,184 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>3.55</v>
       </c>
       <c r="H8" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M8" t="n">
         <v>1.01</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>1.79</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.03</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.92</v>
+        <v>2.74</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99</v>
+        <v>2.78</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>2.82</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR9" t="n">
         <v>16</v>
       </c>
-      <c r="Z9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW9" t="n">
         <v>28</v>
       </c>
-      <c r="AK9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BB9" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="BC9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE9" t="n">
         <v>18</v>
       </c>
-      <c r="BD9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF9" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
@@ -2300,28 +2300,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="G10" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
         <v>3.9</v>
@@ -2330,156 +2330,156 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W10" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.84</v>
-      </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA10" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
         <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS10" t="n">
         <v>13</v>
       </c>
-      <c r="AR10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>10</v>
-      </c>
       <c r="AT10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BF10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,139 +2494,139 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.3</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.7</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC11" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
         <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
         <v>13.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK11" t="n">
         <v>22</v>
       </c>
-      <c r="AI11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>30</v>
-      </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="AT11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU11" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
         <v>13.5</v>
@@ -2635,38 +2635,38 @@
         <v>27</v>
       </c>
       <c r="AX11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC11" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BD11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>34</v>
       </c>
-      <c r="BB11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>32</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
         <v>4.8</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.06</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF12" t="n">
         <v>14</v>
       </c>
-      <c r="Y12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>70</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN12" t="n">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX12" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR12" t="n">
+      <c r="AY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB12" t="n">
         <v>30</v>
       </c>
-      <c r="AS12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BE12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BF12" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="BG12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 17:49:10</t>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,373 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-15 15:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="F14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
         <v>4.4</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="K14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.05</v>
       </c>
-      <c r="N13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="N14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.25</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="P14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.48</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="S14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.83</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>2.14</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="V14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X14" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="Y14" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT14" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="AU14" t="n">
         <v>9</v>
       </c>
-      <c r="AV13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="AV14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC14" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE13" t="n">
+      <c r="BD14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE14" t="n">
         <v>38</v>
       </c>
-      <c r="BF13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>60</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-04-14 17:49:10</t>
+      <c r="BF14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-15 15:11:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -772,13 +772,13 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>1.64</v>
@@ -790,13 +790,13 @@
         <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
@@ -972,19 +972,19 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>1.3</v>
@@ -993,16 +993,16 @@
         <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
@@ -1017,10 +1017,10 @@
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1029,22 +1029,22 @@
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>44</v>
@@ -1053,7 +1053,7 @@
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
         <v>65</v>
@@ -1065,13 +1065,13 @@
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
@@ -1080,41 +1080,41 @@
         <v>14.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
         <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="H4" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1178,25 +1178,25 @@
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
         <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
@@ -1253,7 +1253,7 @@
         <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.6</v>
@@ -1262,53 +1262,53 @@
         <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
         <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BG4" t="n">
         <v>14.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H5" t="n">
         <v>1.93</v>
@@ -1357,7 +1357,7 @@
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1369,22 +1369,22 @@
         <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
         <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
         <v>1.9</v>
@@ -1444,7 +1444,7 @@
         <v>95</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1456,53 +1456,53 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AW5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY5" t="n">
         <v>4</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC5" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
         <v>3.85</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -1539,10 +1539,10 @@
         <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.8</v>
@@ -1557,7 +1557,7 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
@@ -1566,19 +1566,19 @@
         <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
         <v>1.34</v>
@@ -1590,7 +1590,7 @@
         <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
         <v>29</v>
@@ -1629,10 +1629,10 @@
         <v>20</v>
       </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
         <v>12.5</v>
@@ -1650,10 +1650,10 @@
         <v>25</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
@@ -1665,16 +1665,16 @@
         <v>36</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB6" t="n">
         <v>21</v>
@@ -1686,17 +1686,17 @@
         <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF6" t="n">
         <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G7" t="n">
         <v>1.97</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.98</v>
-      </c>
       <c r="H7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I7" t="n">
         <v>4.3</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.41</v>
@@ -1763,7 +1763,7 @@
         <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
         <v>3.4</v>
@@ -1775,7 +1775,7 @@
         <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>2.02</v>
@@ -1793,7 +1793,7 @@
         <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
@@ -1817,7 +1817,7 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
@@ -1871,7 +1871,7 @@
         <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC7" t="n">
         <v>18.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
         <v>3.55</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
         <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="O8" t="n">
         <v>1.68</v>
@@ -1969,7 +1969,7 @@
         <v>1.03</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
         <v>1.39</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G9" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J9" t="n">
         <v>3.5</v>
@@ -2139,34 +2139,34 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.08</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.1</v>
       </c>
       <c r="V9" t="n">
         <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X9" t="n">
         <v>12.5</v>
@@ -2193,40 +2193,40 @@
         <v>32</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AR9" t="n">
         <v>16</v>
@@ -2235,7 +2235,7 @@
         <v>38</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
@@ -2253,7 +2253,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
         <v>40</v>
@@ -2265,20 +2265,20 @@
         <v>29</v>
       </c>
       <c r="BD9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE9" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BG9" t="n">
         <v>26</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2312,16 @@
         <v>1.95</v>
       </c>
       <c r="G10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
         <v>3.9</v>
@@ -2351,16 +2351,16 @@
         <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2375,7 +2375,7 @@
         <v>100</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2429,7 +2429,7 @@
         <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
         <v>7.6</v>
@@ -2450,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB10" t="n">
         <v>19.5</v>
@@ -2462,17 +2462,17 @@
         <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
         <v>2.16</v>
@@ -2512,13 +2512,13 @@
         <v>3.7</v>
       </c>
       <c r="I11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.85</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2533,28 +2533,28 @@
         <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
         <v>1.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
         <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
         <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
         <v>16</v>
@@ -2575,10 +2575,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="n">
         <v>13.5</v>
@@ -2617,7 +2617,7 @@
         <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
         <v>15</v>
@@ -2629,13 +2629,13 @@
         <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY11" t="n">
         <v>9.6</v>
@@ -2644,13 +2644,13 @@
         <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BB11" t="n">
         <v>23</v>
       </c>
       <c r="BC11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I12" t="n">
         <v>3.35</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
@@ -2724,7 +2724,7 @@
         <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
         <v>1.67</v>
@@ -2742,13 +2742,13 @@
         <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
         <v>10</v>
@@ -2772,16 +2772,16 @@
         <v>14.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>70</v>
@@ -2808,7 +2808,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR12" t="n">
         <v>19.5</v>
@@ -2817,40 +2817,40 @@
         <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW12" t="n">
         <v>40</v>
       </c>
       <c r="AX12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY12" t="n">
         <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
         <v>55</v>
       </c>
       <c r="BB12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD12" t="n">
         <v>46</v>
       </c>
       <c r="BE12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF12" t="n">
         <v>26</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.91</v>
       </c>
       <c r="G13" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="n">
         <v>4.6</v>
@@ -2927,7 +2927,7 @@
         <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
         <v>3.6</v>
@@ -2936,13 +2936,13 @@
         <v>1.87</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
         <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -2957,7 +2957,7 @@
         <v>110</v>
       </c>
       <c r="AB13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
@@ -2975,7 +2975,7 @@
         <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
         <v>65</v>
@@ -2993,13 +2993,13 @@
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO13" t="n">
         <v>70</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>15.5</v>
@@ -3017,7 +3017,7 @@
         <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
         <v>50</v>
@@ -3035,7 +3035,7 @@
         <v>55</v>
       </c>
       <c r="BB13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC13" t="n">
         <v>18.5</v>
@@ -3047,14 +3047,14 @@
         <v>40</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
         <v>55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.64</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.66</v>
-      </c>
       <c r="H14" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.36</v>
@@ -3109,7 +3109,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
@@ -3121,64 +3121,64 @@
         <v>1.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U14" t="n">
         <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
         <v>18.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC14" t="n">
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG14" t="n">
         <v>10</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL14" t="n">
         <v>32</v>
@@ -3190,34 +3190,34 @@
         <v>8</v>
       </c>
       <c r="AO14" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP14" t="n">
         <v>17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS14" t="n">
         <v>44</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU14" t="n">
         <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
@@ -3226,13 +3226,13 @@
         <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC14" t="n">
         <v>15</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
         <v>29</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-15 15:11:23</t>
+          <t>2026-04-15 17:24:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
         <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
         <v>3.2</v>
@@ -796,10 +796,10 @@
         <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U2" t="n">
         <v>1.01</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
         <v>4.1</v>
@@ -966,7 +966,7 @@
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -981,7 +981,7 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
         <v>1.87</v>
@@ -993,7 +993,7 @@
         <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
         <v>2</v>
@@ -1002,7 +1002,7 @@
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
@@ -1020,13 +1020,13 @@
         <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
@@ -1038,7 +1038,7 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
@@ -1065,13 +1065,13 @@
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
@@ -1080,7 +1080,7 @@
         <v>14.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1092,7 +1092,7 @@
         <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1101,7 +1101,7 @@
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
         <v>5.5</v>
@@ -1110,11 +1110,11 @@
         <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="n">
         <v>2.44</v>
@@ -1187,28 +1187,28 @@
         <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
         <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
         <v>1.51</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
         <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
         <v>15</v>
@@ -1220,37 +1220,37 @@
         <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
         <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AL4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN4" t="n">
         <v>42</v>
       </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>24</v>
-      </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
         <v>14.5</v>
@@ -1262,53 +1262,53 @@
         <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX4" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>15</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC4" t="n">
         <v>13</v>
       </c>
-      <c r="BA4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
         <v>14.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1339,31 +1339,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G5" t="n">
         <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.38</v>
@@ -1375,76 +1375,76 @@
         <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
         <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
         <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC5" t="n">
         <v>9.6</v>
       </c>
-      <c r="Z5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1456,53 +1456,53 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1533,79 +1533,79 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
         <v>42</v>
@@ -1620,83 +1620,83 @@
         <v>16.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP6" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS6" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BB6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H7" t="n">
         <v>4.2</v>
@@ -1739,10 +1739,10 @@
         <v>4.3</v>
       </c>
       <c r="J7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.41</v>
@@ -1757,19 +1757,19 @@
         <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
         <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
         <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
         <v>2.14</v>
@@ -1778,10 +1778,10 @@
         <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
         <v>16</v>
@@ -1796,7 +1796,7 @@
         <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>17</v>
@@ -1811,7 +1811,7 @@
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
@@ -1823,34 +1823,34 @@
         <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
         <v>15.5</v>
@@ -1862,7 +1862,7 @@
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>17</v>
@@ -1871,26 +1871,26 @@
         <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF7" t="n">
         <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="G8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
         <v>3.05</v>
@@ -1933,10 +1933,10 @@
         <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
@@ -1963,7 +1963,7 @@
         <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="U8" t="n">
         <v>1.03</v>
@@ -1975,7 +1975,7 @@
         <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1990,7 +1990,7 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="G9" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="I9" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="J9" t="n">
         <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,46 +2139,46 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
         <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
         <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="W9" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB9" t="n">
         <v>11</v>
@@ -2187,98 +2187,98 @@
         <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
         <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE9" t="n">
         <v>28</v>
       </c>
-      <c r="AX9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BF9" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BG9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G10" t="n">
         <v>1.98</v>
@@ -2321,7 +2321,7 @@
         <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
         <v>3.9</v>
@@ -2336,25 +2336,25 @@
         <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
         <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
         <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
         <v>1.29</v>
@@ -2363,7 +2363,7 @@
         <v>2.02</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
         <v>16.5</v>
@@ -2408,7 +2408,7 @@
         <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
         <v>14</v>
@@ -2432,13 +2432,13 @@
         <v>8.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
         <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AX10" t="n">
         <v>10.5</v>
@@ -2447,10 +2447,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BB10" t="n">
         <v>19.5</v>
@@ -2462,7 +2462,7 @@
         <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
         <v>3.85</v>
@@ -2533,19 +2533,19 @@
         <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
         <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
         <v>2.24</v>
@@ -2554,10 +2554,10 @@
         <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
@@ -2566,13 +2566,13 @@
         <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
@@ -2581,10 +2581,10 @@
         <v>46</v>
       </c>
       <c r="AF11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2602,7 +2602,7 @@
         <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AN11" t="n">
         <v>15.5</v>
@@ -2614,13 +2614,13 @@
         <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT11" t="n">
         <v>9.6</v>
@@ -2629,22 +2629,22 @@
         <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AX11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BB11" t="n">
         <v>23</v>
@@ -2656,7 +2656,7 @@
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
         <v>13.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.25</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
@@ -2724,31 +2724,31 @@
         <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
         <v>10</v>
@@ -2757,13 +2757,13 @@
         <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
         <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC12" t="n">
         <v>7.2</v>
@@ -2772,7 +2772,7 @@
         <v>14.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
         <v>14.5</v>
@@ -2805,10 +2805,10 @@
         <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12" t="n">
         <v>19.5</v>
@@ -2826,7 +2826,7 @@
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX12" t="n">
         <v>13.5</v>
@@ -2838,7 +2838,7 @@
         <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB12" t="n">
         <v>32</v>
@@ -2850,17 +2850,17 @@
         <v>46</v>
       </c>
       <c r="BE12" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="BF12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BG12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="n">
         <v>1.92</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
         <v>4.8</v>
@@ -2912,28 +2912,28 @@
         <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
         <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
         <v>2.06</v>
@@ -2948,7 +2948,7 @@
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
@@ -2957,7 +2957,7 @@
         <v>110</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
@@ -2978,7 +2978,7 @@
         <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
@@ -2987,7 +2987,7 @@
         <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -3002,16 +3002,16 @@
         <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>30</v>
       </c>
       <c r="AS13" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
@@ -3023,7 +3023,7 @@
         <v>50</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
         <v>9.6</v>
@@ -3035,26 +3035,26 @@
         <v>55</v>
       </c>
       <c r="BB13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC13" t="n">
         <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BF13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I14" t="n">
         <v>6.6</v>
@@ -3100,7 +3100,7 @@
         <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.36</v>
@@ -3115,28 +3115,28 @@
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
         <v>1.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T14" t="n">
         <v>1.82</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X14" t="n">
         <v>18.5</v>
@@ -3187,16 +3187,16 @@
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP14" t="n">
         <v>17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR14" t="n">
         <v>46</v>
@@ -3205,13 +3205,13 @@
         <v>44</v>
       </c>
       <c r="AT14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU14" t="n">
         <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW14" t="n">
         <v>65</v>
@@ -3232,23 +3232,23 @@
         <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
         <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,91 +757,91 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.2</v>
       </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.45</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AC2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE2" t="n">
         <v>500</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -853,7 +853,7 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.18</v>
+        <v>4.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.19</v>
+        <v>5.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.21</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.19</v>
+        <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.18</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.19</v>
+        <v>5.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.21</v>
+        <v>5.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.19</v>
+        <v>5.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.19</v>
+        <v>5.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.21</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.21</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.21</v>
+        <v>6.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.21</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.21</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
@@ -987,22 +987,22 @@
         <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
         <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
@@ -1050,7 +1050,7 @@
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
         <v>17.5</v>
@@ -1068,10 +1068,10 @@
         <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
@@ -1083,10 +1083,10 @@
         <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AZ3" t="n">
         <v>15.5</v>
@@ -1104,7 +1104,7 @@
         <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
         <v>11</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1190,13 +1190,13 @@
         <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
@@ -1232,7 +1232,7 @@
         <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
@@ -1262,13 +1262,13 @@
         <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
@@ -1283,32 +1283,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="BA4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB4" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>4.4</v>
       </c>
-      <c r="BG4" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="I5" t="n">
         <v>2.02</v>
@@ -1390,7 +1390,7 @@
         <v>1.98</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1444,7 +1444,7 @@
         <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1471,38 +1471,38 @@
         <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
         <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>5.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
         <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1566,7 +1566,7 @@
         <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R6" t="n">
         <v>1.41</v>
@@ -1581,7 +1581,7 @@
         <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.87</v>
@@ -1602,13 +1602,13 @@
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1617,16 +1617,16 @@
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
         <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>34</v>
@@ -1647,10 +1647,10 @@
         <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS6" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AT6" t="n">
         <v>9.800000000000001</v>
@@ -1659,7 +1659,7 @@
         <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
         <v>38</v>
@@ -1674,7 +1674,7 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
         <v>22</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1736,10 @@
         <v>4.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
@@ -1772,7 +1772,7 @@
         <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
         <v>1.3</v>
@@ -1832,7 +1832,7 @@
         <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
         <v>14.5</v>
@@ -1886,11 +1886,11 @@
         <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
         <v>4.1</v>
@@ -1936,7 +1936,7 @@
         <v>2.48</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
@@ -1969,10 +1969,10 @@
         <v>1.03</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
         <v>500</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I9" t="n">
         <v>2.62</v>
@@ -2139,34 +2139,34 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
         <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
         <v>13</v>
@@ -2187,25 +2187,25 @@
         <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF9" t="n">
         <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>19</v>
       </c>
       <c r="AI9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>48</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>46</v>
       </c>
       <c r="AK9" t="n">
         <v>36</v>
@@ -2214,25 +2214,25 @@
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="AN9" t="n">
         <v>36</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2253,10 +2253,10 @@
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB9" t="n">
         <v>42</v>
@@ -2268,17 +2268,17 @@
         <v>44</v>
       </c>
       <c r="BE9" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
         <v>32</v>
       </c>
       <c r="BG9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1.98</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
         <v>4.4</v>
@@ -2342,19 +2342,19 @@
         <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
         <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
         <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
         <v>1.29</v>
@@ -2372,13 +2372,13 @@
         <v>34</v>
       </c>
       <c r="AA10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
         <v>17.5</v>
@@ -2396,7 +2396,7 @@
         <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
         <v>23</v>
@@ -2420,13 +2420,13 @@
         <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
         <v>28</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
         <v>8.6</v>
@@ -2435,7 +2435,7 @@
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
         <v>23</v>
@@ -2453,10 +2453,10 @@
         <v>28</v>
       </c>
       <c r="BB10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
         <v>32</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>3.75</v>
@@ -2527,19 +2527,19 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
         <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
         <v>3.3</v>
@@ -2551,19 +2551,19 @@
         <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
         <v>160</v>
@@ -2575,10 +2575,10 @@
         <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
         <v>14</v>
@@ -2590,13 +2590,13 @@
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
         <v>36</v>
@@ -2605,40 +2605,40 @@
         <v>320</v>
       </c>
       <c r="AN11" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
         <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
         <v>15</v>
@@ -2647,26 +2647,26 @@
         <v>36</v>
       </c>
       <c r="BB11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE11" t="n">
         <v>28</v>
       </c>
       <c r="BF11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
         <v>3.4</v>
@@ -2727,10 +2727,10 @@
         <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
         <v>1.25</v>
@@ -2745,13 +2745,13 @@
         <v>1.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
         <v>1.65</v>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
         <v>10.5</v>
@@ -2763,7 +2763,7 @@
         <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC12" t="n">
         <v>7.2</v>
@@ -2808,10 +2808,10 @@
         <v>9.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>55</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.92</v>
       </c>
       <c r="H13" t="n">
         <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.43</v>
@@ -2921,7 +2921,7 @@
         <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
         <v>2.02</v>
@@ -2942,13 +2942,13 @@
         <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
@@ -2957,16 +2957,16 @@
         <v>110</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>11</v>
@@ -3008,10 +3008,10 @@
         <v>30</v>
       </c>
       <c r="AS13" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
@@ -3035,7 +3035,7 @@
         <v>55</v>
       </c>
       <c r="BB13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
         <v>18.5</v>
@@ -3044,7 +3044,7 @@
         <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BF13" t="n">
         <v>12.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
         <v>6.4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6.6</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
@@ -3106,7 +3106,7 @@
         <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
         <v>4.7</v>
@@ -3115,16 +3115,16 @@
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
         <v>1.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T14" t="n">
         <v>1.82</v>
@@ -3133,10 +3133,10 @@
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="X14" t="n">
         <v>18.5</v>
@@ -3157,13 +3157,13 @@
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
         <v>80</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
         <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK14" t="n">
         <v>15.5</v>
@@ -3190,7 +3190,7 @@
         <v>7.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP14" t="n">
         <v>17</v>
@@ -3208,28 +3208,28 @@
         <v>9.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
         <v>65</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
         <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
@@ -3241,14 +3241,14 @@
         <v>55</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG14" t="n">
         <v>75</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -775,7 +775,7 @@
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -787,7 +787,7 @@
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
         <v>2.06</v>
@@ -799,10 +799,10 @@
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>1.52</v>
@@ -820,7 +820,7 @@
         <v>160</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
         <v>120</v>
@@ -844,7 +844,7 @@
         <v>130</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -865,10 +865,10 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
         <v>5.7</v>
@@ -883,7 +883,7 @@
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>6.6</v>
@@ -892,10 +892,10 @@
         <v>5.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA2" t="n">
         <v>7</v>
@@ -910,7 +910,7 @@
         <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
         <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T3" t="n">
         <v>1.81</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.63</v>
       </c>
       <c r="U3" t="n">
         <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
         <v>38</v>
@@ -1017,13 +1017,13 @@
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>60</v>
@@ -1035,19 +1035,19 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>200</v>
@@ -1065,56 +1065,56 @@
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>44</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.9</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
         <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
         <v>9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1157,13 +1157,13 @@
         <v>2.64</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1184,7 +1184,7 @@
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
         <v>1.66</v>
@@ -1268,7 +1268,7 @@
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="I5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1387,7 +1387,7 @@
         <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
         <v>1.25</v>
@@ -1399,13 +1399,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA5" t="n">
         <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
         <v>9.6</v>
@@ -1420,7 +1420,7 @@
         <v>100</v>
       </c>
       <c r="AG5" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>60</v>
@@ -1453,56 +1453,56 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
         <v>2.14</v>
@@ -1542,7 +1542,7 @@
         <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
@@ -1563,7 +1563,7 @@
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
         <v>1.88</v>
@@ -1578,7 +1578,7 @@
         <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
@@ -1593,13 +1593,13 @@
         <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
         <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8.199999999999999</v>
@@ -1623,7 +1623,7 @@
         <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>23</v>
@@ -1650,7 +1650,7 @@
         <v>24</v>
       </c>
       <c r="AS6" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AT6" t="n">
         <v>9.800000000000001</v>
@@ -1674,7 +1674,7 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BB6" t="n">
         <v>22</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.41</v>
@@ -1751,52 +1751,52 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
         <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
         <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB7" t="n">
         <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
         <v>17</v>
@@ -1805,7 +1805,7 @@
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
@@ -1817,10 +1817,10 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
@@ -1829,22 +1829,22 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
@@ -1853,7 +1853,7 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW7" t="n">
         <v>46</v>
@@ -1871,10 +1871,10 @@
         <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD7" t="n">
         <v>32</v>
@@ -1883,14 +1883,14 @@
         <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
         <v>48</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1930,13 +1930,13 @@
         <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
         <v>2.48</v>
       </c>
       <c r="K8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
@@ -1969,7 +1969,7 @@
         <v>1.03</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
         <v>1.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>2.58</v>
       </c>
       <c r="I9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.5</v>
@@ -2139,28 +2139,28 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
         <v>3.95</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
         <v>1.62</v>
@@ -2169,10 +2169,10 @@
         <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
         <v>16</v>
@@ -2181,16 +2181,16 @@
         <v>38</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
         <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="n">
         <v>19.5</v>
@@ -2202,7 +2202,7 @@
         <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
         <v>48</v>
@@ -2211,13 +2211,13 @@
         <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
         <v>27</v>
@@ -2226,7 +2226,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
@@ -2235,7 +2235,7 @@
         <v>32</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
@@ -2244,22 +2244,22 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB9" t="n">
         <v>40</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>42</v>
       </c>
       <c r="BC9" t="n">
         <v>32</v>
@@ -2268,17 +2268,17 @@
         <v>44</v>
       </c>
       <c r="BE9" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="BF9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2309,133 +2309,133 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="G10" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW10" t="n">
         <v>23</v>
@@ -2444,35 +2444,35 @@
         <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
         <v>28</v>
       </c>
       <c r="BB10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BE10" t="n">
         <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2530,19 +2530,19 @@
         <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
         <v>1.76</v>
@@ -2551,122 +2551,122 @@
         <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="X11" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN11" t="n">
         <v>14</v>
       </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>17</v>
-      </c>
       <c r="AO11" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AP11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BF11" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.54</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
         <v>3.45</v>
@@ -2727,7 +2727,7 @@
         <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q12" t="n">
         <v>2.44</v>
@@ -2742,13 +2742,13 @@
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
         <v>9.800000000000001</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2906,13 +2906,13 @@
         <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
         <v>3.8</v>
@@ -2921,7 +2921,7 @@
         <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
         <v>2.02</v>
@@ -2942,13 +2942,13 @@
         <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
@@ -3002,7 +3002,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR13" t="n">
         <v>30</v>
@@ -3020,13 +3020,13 @@
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
@@ -3103,13 +3103,13 @@
         <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
@@ -3124,7 +3124,7 @@
         <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
         <v>1.82</v>
@@ -3136,10 +3136,10 @@
         <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
         <v>24</v>
@@ -3148,16 +3148,16 @@
         <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC14" t="n">
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
         <v>80</v>
@@ -3175,7 +3175,7 @@
         <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK14" t="n">
         <v>15.5</v>
@@ -3190,7 +3190,7 @@
         <v>7.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP14" t="n">
         <v>17</v>
@@ -3208,7 +3208,7 @@
         <v>9.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV14" t="n">
         <v>21</v>
@@ -3220,25 +3220,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BF14" t="n">
         <v>7.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -760,58 +760,58 @@
         <v>2.82</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
         <v>46</v>
@@ -853,74 +853,74 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
         <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
@@ -1020,7 +1020,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>19.5</v>
@@ -1038,13 +1038,13 @@
         <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>42</v>
@@ -1062,7 +1062,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
@@ -1080,13 +1080,13 @@
         <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>16.5</v>
@@ -1101,10 +1101,10 @@
         <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
         <v>12.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -1148,43 +1148,43 @@
         <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H4" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.66</v>
@@ -1193,43 +1193,43 @@
         <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1238,31 +1238,31 @@
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="n">
         <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1271,44 +1271,44 @@
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AW4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC4" t="n">
         <v>13</v>
       </c>
-      <c r="AX4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1363,19 +1363,19 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
         <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
         <v>3.9</v>
@@ -1384,22 +1384,22 @@
         <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
         <v>75</v>
@@ -1408,7 +1408,7 @@
         <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
         <v>11</v>
@@ -1420,13 +1420,13 @@
         <v>100</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AH5" t="n">
         <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AJ5" t="n">
         <v>500</v>
@@ -1441,16 +1441,16 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>40</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
         <v>9.199999999999999</v>
@@ -1462,13 +1462,13 @@
         <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
         <v>6.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX5" t="n">
         <v>14.5</v>
@@ -1483,26 +1483,26 @@
         <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BG5" t="n">
         <v>13.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -1542,43 +1542,43 @@
         <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
@@ -1590,7 +1590,7 @@
         <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
         <v>28</v>
@@ -1599,7 +1599,7 @@
         <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
         <v>8.199999999999999</v>
@@ -1614,19 +1614,19 @@
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>34</v>
@@ -1635,10 +1635,10 @@
         <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP6" t="n">
         <v>15.5</v>
@@ -1650,13 +1650,13 @@
         <v>24</v>
       </c>
       <c r="AS6" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>13.5</v>
@@ -1668,13 +1668,13 @@
         <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BB6" t="n">
         <v>22</v>
@@ -1689,14 +1689,14 @@
         <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG6" t="n">
         <v>34</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I7" t="n">
         <v>4.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.5</v>
       </c>
       <c r="J7" t="n">
         <v>3.85</v>
@@ -1760,7 +1760,7 @@
         <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R7" t="n">
         <v>1.41</v>
@@ -1769,16 +1769,16 @@
         <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
@@ -1799,16 +1799,16 @@
         <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
         <v>18</v>
@@ -1817,7 +1817,7 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
         <v>19</v>
@@ -1826,7 +1826,7 @@
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
         <v>12.5</v>
@@ -1862,16 +1862,16 @@
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
         <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>18</v>
@@ -1880,17 +1880,17 @@
         <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG7" t="n">
         <v>48</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="G8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.05</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
         <v>1.03</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>500</v>
+        <v>6.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.45</v>
+        <v>5.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.58</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.47</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.48</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.56</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.59</v>
+        <v>14.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.55</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.62</v>
+        <v>8.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.62</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.61</v>
+        <v>8.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.61</v>
+        <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I9" t="n">
         <v>2.58</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.5</v>
@@ -2133,46 +2133,46 @@
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.08</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9" t="n">
         <v>16</v>
@@ -2181,16 +2181,16 @@
         <v>38</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
         <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF9" t="n">
         <v>19.5</v>
@@ -2202,40 +2202,40 @@
         <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK9" t="n">
         <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
@@ -2247,19 +2247,19 @@
         <v>26</v>
       </c>
       <c r="AX9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC9" t="n">
         <v>32</v>
@@ -2268,17 +2268,17 @@
         <v>44</v>
       </c>
       <c r="BE9" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G10" t="n">
         <v>1.85</v>
@@ -2321,40 +2321,40 @@
         <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
@@ -2363,19 +2363,19 @@
         <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y10" t="n">
         <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>9</v>
@@ -2384,7 +2384,7 @@
         <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
         <v>11.5</v>
@@ -2402,16 +2402,16 @@
         <v>19.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
         <v>60</v>
@@ -2420,22 +2420,22 @@
         <v>15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR10" t="n">
         <v>32</v>
       </c>
       <c r="AS10" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AT10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>23</v>
@@ -2447,10 +2447,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BB10" t="n">
         <v>18</v>
@@ -2459,20 +2459,20 @@
         <v>16.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG10" t="n">
         <v>50</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -2503,85 +2503,85 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
         <v>1.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
         <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -2590,25 +2590,25 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
         <v>15.5</v>
@@ -2617,34 +2617,34 @@
         <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -2659,14 +2659,14 @@
         <v>44</v>
       </c>
       <c r="BF11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
@@ -2724,7 +2724,7 @@
         <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
         <v>1.68</v>
@@ -2736,13 +2736,13 @@
         <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V12" t="n">
         <v>1.41</v>
@@ -2811,7 +2811,7 @@
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>55</v>
@@ -2844,7 +2844,7 @@
         <v>32</v>
       </c>
       <c r="BC12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
         <v>46</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H13" t="n">
         <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
@@ -2909,7 +2909,7 @@
         <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -2921,10 +2921,10 @@
         <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
@@ -2933,7 +2933,7 @@
         <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U13" t="n">
         <v>2.06</v>
@@ -2948,7 +2948,7 @@
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
@@ -2963,7 +2963,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
@@ -2972,7 +2972,7 @@
         <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
         <v>19.5</v>
@@ -3002,7 +3002,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
         <v>30</v>
@@ -3029,7 +3029,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
         <v>55</v>
@@ -3041,7 +3041,7 @@
         <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE13" t="n">
         <v>65</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I14" t="n">
         <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.35</v>
@@ -3115,31 +3115,31 @@
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y14" t="n">
         <v>24</v>
@@ -3151,31 +3151,31 @@
         <v>170</v>
       </c>
       <c r="AB14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC14" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG14" t="n">
         <v>10</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>15.5</v>
@@ -3187,22 +3187,22 @@
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO14" t="n">
         <v>110</v>
       </c>
       <c r="AP14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>22</v>
       </c>
       <c r="AR14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS14" t="n">
         <v>46</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>44</v>
       </c>
       <c r="AT14" t="n">
         <v>9.4</v>
@@ -3211,19 +3211,19 @@
         <v>9.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW14" t="n">
         <v>65</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
         <v>60</v>
@@ -3235,20 +3235,20 @@
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-16 00:04:54</t>
+          <t>2026-04-16 02:22:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G2" t="n">
         <v>3.05</v>
@@ -766,49 +766,49 @@
         <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
         <v>26</v>
@@ -829,7 +829,7 @@
         <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
@@ -859,68 +859,68 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AU2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX2" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD2" t="n">
         <v>7.8</v>
       </c>
-      <c r="BD2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>2.64</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
         <v>7.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -984,49 +984,49 @@
         <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
@@ -1035,86 +1035,86 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
         <v>20</v>
       </c>
       <c r="AX3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>10</v>
       </c>
-      <c r="AY3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>9</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
         <v>2.5</v>
@@ -1157,49 +1157,49 @@
         <v>2.66</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
         <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
         <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
         <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
         <v>20</v>
@@ -1208,19 +1208,19 @@
         <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
         <v>38</v>
@@ -1229,19 +1229,19 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
@@ -1253,7 +1253,7 @@
         <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.6</v>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1271,16 +1271,16 @@
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>13.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>9</v>
@@ -1295,20 +1295,20 @@
         <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1339,79 +1339,79 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="I5" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
         <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W5" t="n">
         <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
         <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
         <v>65</v>
@@ -1420,13 +1420,13 @@
         <v>100</v>
       </c>
       <c r="AG5" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>500</v>
@@ -1444,65 +1444,65 @@
         <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX5" t="n">
         <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE5" t="n">
+      <c r="BF5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>10</v>
       </c>
-      <c r="BF5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1539,58 +1539,58 @@
         <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y6" t="n">
         <v>16.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>16</v>
       </c>
       <c r="Z6" t="n">
         <v>28</v>
@@ -1599,104 +1599,104 @@
         <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR6" t="n">
         <v>24</v>
       </c>
       <c r="AS6" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
         <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H7" t="n">
         <v>4.3</v>
@@ -1739,22 +1739,22 @@
         <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
         <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
         <v>2.06</v>
@@ -1769,7 +1769,7 @@
         <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
         <v>2.16</v>
@@ -1778,19 +1778,19 @@
         <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA7" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
         <v>9.4</v>
@@ -1799,16 +1799,16 @@
         <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
         <v>18</v>
@@ -1820,37 +1820,37 @@
         <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>15.5</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
         <v>16</v>
@@ -1871,7 +1871,7 @@
         <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
         <v>18</v>
@@ -1880,17 +1880,17 @@
         <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -1921,40 +1921,40 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
         <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
         <v>2.62</v>
       </c>
       <c r="K8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M8" t="n">
         <v>1.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="P8" t="n">
         <v>1.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
@@ -1966,13 +1966,13 @@
         <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
         <v>6.6</v>
@@ -1981,19 +1981,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE8" t="n">
         <v>210</v>
@@ -2002,7 +2002,7 @@
         <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
         <v>32</v>
@@ -2014,7 +2014,7 @@
         <v>130</v>
       </c>
       <c r="AK8" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="n">
         <v>250</v>
@@ -2038,19 +2038,19 @@
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="AX8" t="n">
         <v>14.5</v>
@@ -2059,32 +2059,32 @@
         <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG8" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="J9" t="n">
         <v>3.5</v>
@@ -2133,7 +2133,7 @@
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
@@ -2142,73 +2142,73 @@
         <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
         <v>46</v>
       </c>
       <c r="AJ9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
@@ -2217,68 +2217,68 @@
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
         <v>26</v>
       </c>
       <c r="AX9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
         <v>40</v>
       </c>
       <c r="BB9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BC9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BE9" t="n">
         <v>95</v>
       </c>
       <c r="BF9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BG9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.83</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.85</v>
       </c>
       <c r="H10" t="n">
         <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.38</v>
@@ -2339,10 +2339,10 @@
         <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R10" t="n">
         <v>1.45</v>
@@ -2351,7 +2351,7 @@
         <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
         <v>2.18</v>
@@ -2360,16 +2360,16 @@
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
         <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
         <v>110</v>
@@ -2402,13 +2402,13 @@
         <v>19.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL10" t="n">
         <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
         <v>10.5</v>
@@ -2417,19 +2417,19 @@
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR10" t="n">
         <v>32</v>
       </c>
       <c r="AS10" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
         <v>8.4</v>
@@ -2447,16 +2447,16 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
         <v>29</v>
@@ -2465,14 +2465,14 @@
         <v>75</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG10" t="n">
         <v>50</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2503,31 +2503,31 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.29</v>
@@ -2542,46 +2542,46 @@
         <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
         <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -2593,7 +2593,7 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK11" t="n">
         <v>21</v>
@@ -2605,13 +2605,13 @@
         <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
         <v>13.5</v>
@@ -2620,7 +2620,7 @@
         <v>25</v>
       </c>
       <c r="AS11" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -2629,28 +2629,28 @@
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2706,13 +2706,13 @@
         <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.53</v>
@@ -2745,13 +2745,13 @@
         <v>1.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
         <v>1.64</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y12" t="n">
         <v>10.5</v>
@@ -2763,16 +2763,16 @@
         <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
         <v>14.5</v>
@@ -2781,10 +2781,10 @@
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="n">
         <v>36</v>
@@ -2802,10 +2802,10 @@
         <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>10</v>
@@ -2835,32 +2835,32 @@
         <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB12" t="n">
         <v>32</v>
       </c>
       <c r="BC12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE12" t="n">
         <v>110</v>
       </c>
       <c r="BF12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG12" t="n">
         <v>50</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="n">
         <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
@@ -2909,19 +2909,19 @@
         <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
         <v>2.04</v>
@@ -2930,10 +2930,10 @@
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
         <v>2.06</v>
@@ -2945,7 +2945,7 @@
         <v>2.08</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
         <v>16</v>
@@ -2984,7 +2984,7 @@
         <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL13" t="n">
         <v>38</v>
@@ -2999,10 +2999,10 @@
         <v>70</v>
       </c>
       <c r="AP13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR13" t="n">
         <v>30</v>
@@ -3023,7 +3023,7 @@
         <v>55</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
         <v>9.800000000000001</v>
@@ -3032,7 +3032,7 @@
         <v>18.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB13" t="n">
         <v>19</v>
@@ -3041,20 +3041,20 @@
         <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE13" t="n">
         <v>65</v>
       </c>
       <c r="BF13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
         <v>60</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>
@@ -3097,10 +3097,10 @@
         <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.35</v>
@@ -3109,37 +3109,37 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="X14" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="n">
         <v>24</v>
@@ -3151,16 +3151,16 @@
         <v>170</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF14" t="n">
         <v>9.800000000000001</v>
@@ -3172,43 +3172,43 @@
         <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK14" t="n">
         <v>15</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>15.5</v>
       </c>
       <c r="AL14" t="n">
         <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO14" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AP14" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>22</v>
       </c>
       <c r="AR14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AS14" t="n">
         <v>46</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV14" t="n">
         <v>22</v>
@@ -3217,10 +3217,10 @@
         <v>65</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
         <v>19</v>
@@ -3238,17 +3238,17 @@
         <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-16 02:22:16</t>
+          <t>2026-04-16 04:40:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G2" t="n">
         <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
         <v>3.4</v>
       </c>
-      <c r="K2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.85</v>
-      </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA2" t="n">
         <v>160</v>
       </c>
-      <c r="AA2" t="n">
-        <v>500</v>
-      </c>
       <c r="AB2" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG2" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AH2" t="n">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.64</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG2" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
         <v>4.1</v>
@@ -966,67 +966,67 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
         <v>1.94</v>
       </c>
       <c r="X3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y3" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
@@ -1035,86 +1035,86 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO3" t="n">
         <v>65</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>110</v>
-      </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AT3" t="n">
         <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
         <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I4" t="n">
         <v>2.66</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.37</v>
@@ -1169,13 +1169,13 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
         <v>1.83</v>
@@ -1184,13 +1184,13 @@
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.6</v>
@@ -1199,10 +1199,10 @@
         <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
         <v>970</v>
@@ -1211,104 +1211,104 @@
         <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
         <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="AO4" t="n">
         <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU4" t="n">
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BD4" t="n">
         <v>18</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
@@ -1363,146 +1363,146 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
         <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
         <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
         <v>8.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AH5" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AJ5" t="n">
         <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
         <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AX5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
       <c r="BA5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.6</v>
+        <v>60</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>3.9</v>
@@ -1551,7 +1551,7 @@
         <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1563,31 +1563,31 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
         <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
         <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
         <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.89</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
         <v>16.5</v>
@@ -1596,58 +1596,58 @@
         <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
         <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>15</v>
       </c>
       <c r="AR6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS6" t="n">
         <v>55</v>
@@ -1656,7 +1656,7 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>13.5</v>
@@ -1668,10 +1668,10 @@
         <v>13</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
         <v>40</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.96</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H7" t="n">
         <v>4.3</v>
@@ -1742,10 +1742,10 @@
         <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -1769,7 +1769,7 @@
         <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
         <v>2.16</v>
@@ -1784,22 +1784,22 @@
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
         <v>30</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="n">
         <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
         <v>50</v>
@@ -1817,43 +1817,43 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>19.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
       </c>
       <c r="AP7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>15</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>14.5</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW7" t="n">
         <v>46</v>
@@ -1862,16 +1862,16 @@
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
         <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC7" t="n">
         <v>18</v>
@@ -1880,17 +1880,17 @@
         <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
         <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J8" t="n">
         <v>2.62</v>
       </c>
       <c r="K8" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="L8" t="n">
         <v>1.76</v>
@@ -1948,52 +1948,52 @@
         <v>2.16</v>
       </c>
       <c r="O8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="P8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T8" t="n">
         <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V8" t="n">
         <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
         <v>6.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="n">
         <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>210</v>
@@ -2002,7 +2002,7 @@
         <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH8" t="n">
         <v>32</v>
@@ -2011,10 +2011,10 @@
         <v>290</v>
       </c>
       <c r="AJ8" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AK8" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AL8" t="n">
         <v>250</v>
@@ -2023,10 +2023,10 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
         <v>5.5</v>
@@ -2035,10 +2035,10 @@
         <v>6.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="AT8" t="n">
         <v>6.2</v>
@@ -2050,7 +2050,7 @@
         <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX8" t="n">
         <v>14.5</v>
@@ -2059,32 +2059,32 @@
         <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG8" t="n">
         <v>10</v>
       </c>
-      <c r="BE8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -2115,79 +2115,79 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
         <v>2.42</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.48</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
         <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X9" t="n">
         <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z9" t="n">
         <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
         <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>27</v>
@@ -2199,16 +2199,16 @@
         <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
         <v>60</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
@@ -2217,10 +2217,10 @@
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
@@ -2229,7 +2229,7 @@
         <v>8.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2244,7 +2244,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
         <v>20</v>
@@ -2253,13 +2253,13 @@
         <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BC9" t="n">
         <v>36</v>
@@ -2271,14 +2271,14 @@
         <v>95</v>
       </c>
       <c r="BF9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
@@ -2339,10 +2339,10 @@
         <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
         <v>1.45</v>
@@ -2357,22 +2357,22 @@
         <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X10" t="n">
         <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB10" t="n">
         <v>9.800000000000001</v>
@@ -2384,16 +2384,16 @@
         <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
         <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
         <v>60</v>
@@ -2402,19 +2402,19 @@
         <v>19.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
         <v>10.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
         <v>15.5</v>
@@ -2426,7 +2426,7 @@
         <v>32</v>
       </c>
       <c r="AS10" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
@@ -2438,22 +2438,22 @@
         <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AX10" t="n">
         <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC10" t="n">
         <v>16</v>
@@ -2465,14 +2465,14 @@
         <v>75</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.04</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.08</v>
-      </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K11" t="n">
         <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.39</v>
@@ -2527,49 +2527,49 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
         <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
         <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>8.6</v>
@@ -2578,7 +2578,7 @@
         <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="n">
         <v>13</v>
@@ -2587,16 +2587,16 @@
         <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
@@ -2605,7 +2605,7 @@
         <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO11" t="n">
         <v>44</v>
@@ -2614,13 +2614,13 @@
         <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS11" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -2629,16 +2629,16 @@
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
         <v>16</v>
@@ -2650,13 +2650,13 @@
         <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BF11" t="n">
         <v>12</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
@@ -2739,19 +2739,19 @@
         <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
         <v>10.5</v>
@@ -2760,7 +2760,7 @@
         <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
         <v>8.199999999999999</v>
@@ -2769,19 +2769,19 @@
         <v>7</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
         <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>65</v>
@@ -2790,7 +2790,7 @@
         <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
@@ -2802,13 +2802,13 @@
         <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12" t="n">
         <v>20</v>
@@ -2826,13 +2826,13 @@
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX12" t="n">
         <v>13.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>19.5</v>
@@ -2844,13 +2844,13 @@
         <v>32</v>
       </c>
       <c r="BC12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD12" t="n">
         <v>48</v>
       </c>
       <c r="BE12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF12" t="n">
         <v>29</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H13" t="n">
         <v>4.7</v>
@@ -2912,16 +2912,16 @@
         <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
         <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
         <v>2.04</v>
@@ -2933,7 +2933,7 @@
         <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
         <v>2.06</v>
@@ -2945,7 +2945,7 @@
         <v>2.08</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
         <v>16</v>
@@ -2957,7 +2957,7 @@
         <v>110</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
@@ -2972,19 +2972,19 @@
         <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="n">
         <v>38</v>
@@ -2996,22 +2996,22 @@
         <v>13.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
         <v>30</v>
       </c>
       <c r="AS13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
@@ -3023,13 +3023,13 @@
         <v>55</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
         <v>60</v>
@@ -3038,23 +3038,23 @@
         <v>19</v>
       </c>
       <c r="BC13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BF13" t="n">
         <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.6</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.61</v>
-      </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
         <v>6.6</v>
@@ -3100,10 +3100,10 @@
         <v>4.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3112,10 +3112,10 @@
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
         <v>1.73</v>
@@ -3124,22 +3124,22 @@
         <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
         <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
         <v>24</v>
@@ -3148,7 +3148,7 @@
         <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB14" t="n">
         <v>10</v>
@@ -3157,25 +3157,25 @@
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
         <v>80</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
         <v>10</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>15</v>
@@ -3190,10 +3190,10 @@
         <v>7.2</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ14" t="n">
         <v>22</v>
@@ -3202,10 +3202,10 @@
         <v>48</v>
       </c>
       <c r="AS14" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
         <v>9.6</v>
@@ -3217,38 +3217,38 @@
         <v>65</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
         <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG14" t="n">
         <v>75</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-16 04:40:51</t>
+          <t>2026-04-16 07:00:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.82</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>990</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>60</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>230</v>
+        <v>550</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>28</v>
+        <v>2.24</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>2.36</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>3.05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>2.52</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>3.05</v>
       </c>
       <c r="BD2" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>1.71</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.43</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC3" t="n">
         <v>21</v>
       </c>
-      <c r="BC3" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H4" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="I4" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.37</v>
@@ -1169,82 +1169,82 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
         <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
         <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
         <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
         <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
         <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>42</v>
@@ -1256,59 +1256,59 @@
         <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
         <v>19.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
         <v>18</v>
       </c>
       <c r="BE4" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>38</v>
       </c>
       <c r="AF5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI5" t="n">
         <v>50</v>
       </c>
-      <c r="AG5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>370</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN5" t="n">
         <v>180</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>370</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>95</v>
-      </c>
       <c r="AO5" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
         <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AT5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY5" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BD5" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE5" t="n">
         <v>28</v>
       </c>
-      <c r="BE5" t="n">
-        <v>10</v>
-      </c>
       <c r="BF5" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.38</v>
@@ -1557,153 +1557,153 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
         <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>32</v>
       </c>
       <c r="AM6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN6" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6" t="n">
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
         <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
         <v>19</v>
       </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>2.64</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>2.82</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>2.18</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>1.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="T7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X7" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BA7" t="n">
         <v>1.84</v>
       </c>
-      <c r="U7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="BB7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE7" t="n">
         <v>2.02</v>
       </c>
-      <c r="X7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>75</v>
-      </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>1.84</v>
       </c>
       <c r="BG7" t="n">
-        <v>48</v>
+        <v>2.02</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,184 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.45</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.16</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC8" t="n">
         <v>7.8</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU8" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>210</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>250</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AX8" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
         <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>95</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.6</v>
+        <v>38</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>1.79</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.42</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC9" t="n">
         <v>9.4</v>
       </c>
-      <c r="Z9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL9" t="n">
         <v>32</v>
       </c>
-      <c r="AB9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AM9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO9" t="n">
         <v>60</v>
       </c>
-      <c r="AK9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>24</v>
-      </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AV9" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BB9" t="n">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG9" t="n">
         <v>50</v>
       </c>
-      <c r="BE9" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>21</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.39</v>
@@ -2333,76 +2333,76 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>34</v>
@@ -2411,75 +2411,75 @@
         <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AS10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB10" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE10" t="n">
         <v>75</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.42</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR11" t="n">
         <v>20</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AS11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB11" t="n">
         <v>34</v>
       </c>
-      <c r="AM11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>21</v>
-      </c>
       <c r="BC11" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BE11" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BG11" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.52</v>
+        <v>1.93</v>
       </c>
       <c r="G12" t="n">
-        <v>2.54</v>
+        <v>1.94</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE12" t="n">
         <v>65</v>
       </c>
-      <c r="AB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>44</v>
-      </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
         <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR12" t="n">
         <v>30</v>
       </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>20</v>
-      </c>
       <c r="AS12" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AT12" t="n">
         <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF12" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>29</v>
-      </c>
       <c r="BG12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>
@@ -2882,373 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Z13" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO13" t="n">
         <v>110</v>
       </c>
-      <c r="AB13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AP13" t="n">
         <v>18</v>
       </c>
-      <c r="AE13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI13" t="n">
+      <c r="AQ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW13" t="n">
         <v>70</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>55</v>
-      </c>
       <c r="AX13" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY13" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BB13" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BE13" t="n">
         <v>90</v>
       </c>
       <c r="BF13" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-16 07:00:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>UEFA Europa League</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X14" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>75</v>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-04-16 07:00:30</t>
+          <t>2026-04-16 09:32:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Shirak</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BKMA Yerevan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y2" t="n">
         <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
         <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>990</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>990</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>990</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>990</v>
+        <v>46</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>550</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AP2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AR2" t="n">
-        <v>3.4</v>
+        <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.24</v>
+        <v>120</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.05</v>
+        <v>23</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.36</v>
+        <v>110</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.05</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.3</v>
+        <v>36</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.9</v>
+        <v>160</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.52</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.05</v>
+        <v>34</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.1</v>
+        <v>90</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.1</v>
+        <v>220</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.71</v>
+        <v>46</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.18</v>
+        <v>150</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2.44</v>
       </c>
       <c r="I3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
         <v>4.4</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG3" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN3" t="n">
         <v>26</v>
       </c>
-      <c r="AL3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23</v>
-      </c>
       <c r="AO3" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
         <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB3" t="n">
         <v>44</v>
       </c>
-      <c r="BB3" t="n">
-        <v>23</v>
-      </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BD3" t="n">
         <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BG3" t="n">
-        <v>55</v>
+        <v>16.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.84</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.37</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.54</v>
-      </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="AX4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="BC4" t="n">
         <v>25</v>
       </c>
       <c r="BD4" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="BE4" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="BF4" t="n">
-        <v>18.5</v>
+        <v>46</v>
       </c>
       <c r="BG4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.3</v>
+        <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>1.99</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AU5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB5" t="n">
         <v>24</v>
       </c>
-      <c r="AB5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>370</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="BC5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>27</v>
       </c>
-      <c r="AY5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>18</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AS6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BB6" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD6" t="n">
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BF6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="G7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H7" t="n">
         <v>3.3</v>
       </c>
-      <c r="H7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L7" t="n">
         <v>1.76</v>
       </c>
       <c r="M7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="N7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T7" t="n">
         <v>1.05</v>
@@ -1775,16 +1775,16 @@
         <v>1.03</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y7" t="n">
         <v>500</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AC7" t="n">
         <v>1000</v>
@@ -1844,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AT7" t="n">
         <v>3.4</v>
@@ -1856,41 +1856,41 @@
         <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.9</v>
+        <v>1.78</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -1951,28 +1951,28 @@
         <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
         <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -1984,16 +1984,16 @@
         <v>14.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
         <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>27</v>
@@ -2002,7 +2002,7 @@
         <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
         <v>19</v>
@@ -2014,34 +2014,34 @@
         <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN8" t="n">
         <v>44</v>
       </c>
       <c r="AO8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
         <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
         <v>7.4</v>
@@ -2050,25 +2050,25 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC8" t="n">
         <v>38</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>36</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
@@ -2080,11 +2080,11 @@
         <v>38</v>
       </c>
       <c r="BG8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
         <v>2.18</v>
@@ -2157,7 +2157,7 @@
         <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
         <v>2.18</v>
@@ -2178,16 +2178,16 @@
         <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
         <v>60</v>
@@ -2202,16 +2202,16 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
         <v>17.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>90</v>
@@ -2223,10 +2223,10 @@
         <v>60</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
         <v>32</v>
@@ -2241,10 +2241,10 @@
         <v>8.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
         <v>50</v>
       </c>
       <c r="BB9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2271,14 +2271,14 @@
         <v>75</v>
       </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
         <v>50</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>2.04</v>
       </c>
       <c r="H10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I10" t="n">
         <v>3.95</v>
       </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
       <c r="J10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.95</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.39</v>
@@ -2333,13 +2333,13 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
         <v>1.87</v>
@@ -2351,37 +2351,37 @@
         <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V10" t="n">
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
         <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
         <v>44</v>
@@ -2396,7 +2396,7 @@
         <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
         <v>23</v>
@@ -2408,31 +2408,31 @@
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
         <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
         <v>15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>26</v>
       </c>
       <c r="AS10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
         <v>14.5</v>
@@ -2441,16 +2441,16 @@
         <v>40</v>
       </c>
       <c r="AX10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2468,11 +2468,11 @@
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H11" t="n">
         <v>3.3</v>
@@ -2533,10 +2533,10 @@
         <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -2545,49 +2545,49 @@
         <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
         <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>65</v>
@@ -2599,16 +2599,16 @@
         <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
         <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
         <v>9.6</v>
@@ -2641,7 +2641,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>55</v>
@@ -2653,10 +2653,10 @@
         <v>28</v>
       </c>
       <c r="BD11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BF11" t="n">
         <v>29</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G12" t="n">
         <v>1.93</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.94</v>
       </c>
       <c r="H12" t="n">
         <v>4.7</v>
@@ -2715,7 +2715,7 @@
         <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -2727,7 +2727,7 @@
         <v>1.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
         <v>2.12</v>
@@ -2736,13 +2736,13 @@
         <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
         <v>1.26</v>
@@ -2763,10 +2763,10 @@
         <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
         <v>18.5</v>
@@ -2790,7 +2790,7 @@
         <v>21</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>38</v>
@@ -2799,7 +2799,7 @@
         <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>85</v>
@@ -2817,10 +2817,10 @@
         <v>95</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
         <v>17</v>
@@ -2841,10 +2841,10 @@
         <v>65</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>34</v>
@@ -2856,11 +2856,11 @@
         <v>13.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H13" t="n">
         <v>6.2</v>
@@ -2903,52 +2903,52 @@
         <v>6.4</v>
       </c>
       <c r="J13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.5</v>
       </c>
-      <c r="K13" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z13" t="n">
         <v>48</v>
@@ -2957,7 +2957,7 @@
         <v>170</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>9.6</v>
@@ -2966,10 +2966,10 @@
         <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG13" t="n">
         <v>10</v>
@@ -2993,25 +2993,25 @@
         <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS13" t="n">
         <v>150</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
         <v>9.4</v>
@@ -3020,22 +3020,22 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
         <v>70</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
         <v>14.5</v>
@@ -3044,17 +3044,17 @@
         <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-16 09:32:49</t>
+          <t>2026-04-16 12:03:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H2" t="n">
         <v>3.05</v>
       </c>
-      <c r="H2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>7</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S2" t="n">
-        <v>18</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>400</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>310</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV2" t="n">
+      <c r="BA2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD2" t="n">
         <v>21</v>
       </c>
-      <c r="AW2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>150</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>70</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>150</v>
-      </c>
       <c r="BE2" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="BG2" t="n">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-16 14:36:03</t>
+          <t>2026-04-16 17:08:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>3.65</v>
       </c>
-      <c r="G3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BB3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD3" t="n">
         <v>25</v>
       </c>
-      <c r="BA3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>100</v>
       </c>
       <c r="BF3" t="n">
         <v>4.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-16 14:36:03</t>
+          <t>2026-04-16 17:08:23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,960 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CD Victoria</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.22</v>
+        <v>95</v>
       </c>
       <c r="I4" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="J4" t="n">
-        <v>2.12</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.42</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
+        <v>16</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>120</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>250</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:08:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>36</v>
+      </c>
+      <c r="I5" t="n">
+        <v>38</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>360</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>540</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>210</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>370</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>400</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:08:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:08:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>1.01</v>
       </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
+      <c r="G7" t="n">
         <v>1.01</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="H7" t="n">
+        <v>700</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>120</v>
+      </c>
+      <c r="K7" t="n">
+        <v>140</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.01</v>
       </c>
-      <c r="AR4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:36:03</t>
+      <c r="W7" t="n">
+        <v>100</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:08:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CD Victoria</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:08:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-16.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
         <v>5.2</v>
@@ -781,31 +781,31 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
         <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="W2" t="n">
         <v>1.15</v>
@@ -814,113 +814,113 @@
         <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AB2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.72</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.12</v>
+        <v>17</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.83</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.76</v>
+        <v>18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.75</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.8</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.86</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.85</v>
+        <v>44</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.84</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.85</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.85</v>
+        <v>34</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-16 19:40:47</t>
+          <t>2026-04-16 22:13:15</t>
         </is>
       </c>
     </row>
